--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mh_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mh_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -826,7 +826,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -14005,7 +14005,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14470,7 +14470,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14749,7 +14749,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17869,7 +17869,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -18241,7 +18241,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18613,7 +18613,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18892,7 +18892,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19543,7 +19543,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -20101,7 +20101,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20473,7 +20473,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -21124,7 +21124,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21589,7 +21589,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -22054,7 +22054,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -22147,7 +22147,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22339,7 +22339,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22731,7 +22731,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22917,7 +22917,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -23103,7 +23103,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23196,7 +23196,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23289,7 +23289,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23382,7 +23382,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23754,7 +23754,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23847,7 +23847,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -24033,7 +24033,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -24126,7 +24126,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -24219,7 +24219,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -24312,7 +24312,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24688,7 +24688,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr"/>
@@ -24882,7 +24882,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr"/>
@@ -24979,7 +24979,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -25076,7 +25076,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -25173,7 +25173,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -25270,7 +25270,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr"/>
@@ -25367,7 +25367,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr"/>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25658,7 +25658,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25755,7 +25755,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26351,7 +26351,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26448,7 +26448,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26545,7 +26545,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26933,7 +26933,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -27127,7 +27127,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -27321,7 +27321,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -27418,7 +27418,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27515,7 +27515,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27608,7 +27608,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="inlineStr"/>
@@ -27794,7 +27794,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -27986,7 +27986,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -28172,7 +28172,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -28265,7 +28265,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28544,7 +28544,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28730,7 +28730,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28823,7 +28823,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28916,7 +28916,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -29009,7 +29009,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -29102,7 +29102,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -29195,7 +29195,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -29288,7 +29288,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -29381,7 +29381,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29474,7 +29474,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29567,7 +29567,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="inlineStr"/>
@@ -29660,7 +29660,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="inlineStr"/>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="inlineStr"/>
@@ -29939,7 +29939,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="inlineStr"/>
@@ -30032,7 +30032,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -30404,7 +30404,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30780,7 +30780,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -31168,7 +31168,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="inlineStr"/>
@@ -31362,7 +31362,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -31459,7 +31459,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="inlineStr"/>
@@ -31556,7 +31556,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -31653,7 +31653,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="inlineStr"/>
@@ -31750,7 +31750,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31847,7 +31847,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -31944,7 +31944,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -32041,7 +32041,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -32235,7 +32235,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -32332,7 +32332,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32914,7 +32914,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -33100,7 +33100,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="n">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="n">
@@ -33298,7 +33298,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33391,7 +33391,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33484,7 +33484,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="n">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="n">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33971,7 +33971,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -34064,7 +34064,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="inlineStr"/>
@@ -34250,7 +34250,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="inlineStr"/>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="inlineStr"/>
@@ -34622,7 +34622,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="inlineStr"/>
@@ -34715,7 +34715,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="inlineStr"/>
@@ -34808,7 +34808,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="inlineStr"/>
@@ -34901,7 +34901,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="inlineStr"/>
@@ -34994,7 +34994,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="inlineStr"/>
@@ -35087,7 +35087,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="inlineStr"/>
@@ -35180,7 +35180,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="inlineStr"/>
@@ -35273,7 +35273,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="inlineStr"/>
@@ -35459,7 +35459,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="inlineStr"/>
@@ -35552,7 +35552,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -35831,7 +35831,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -35924,7 +35924,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -36110,7 +36110,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -36203,7 +36203,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36482,7 +36482,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36575,7 +36575,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36672,7 +36672,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36866,7 +36866,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -36963,7 +36963,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -37060,7 +37060,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -37157,7 +37157,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -37254,7 +37254,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -37351,7 +37351,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -37448,7 +37448,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37642,7 +37642,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="inlineStr"/>
@@ -37739,7 +37739,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="inlineStr"/>
@@ -37832,7 +37832,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="inlineStr"/>
@@ -37925,7 +37925,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="inlineStr"/>
@@ -38018,7 +38018,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="inlineStr"/>
@@ -38111,7 +38111,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="inlineStr"/>
@@ -38204,7 +38204,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="inlineStr"/>
@@ -38297,7 +38297,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="inlineStr"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="inlineStr"/>
@@ -38483,7 +38483,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="inlineStr"/>
@@ -38576,7 +38576,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="inlineStr"/>
@@ -38762,7 +38762,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="inlineStr"/>
@@ -38855,7 +38855,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="inlineStr"/>
@@ -38948,7 +38948,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="inlineStr"/>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="inlineStr"/>
@@ -39134,7 +39134,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="inlineStr"/>
@@ -39227,7 +39227,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="inlineStr"/>
@@ -39320,7 +39320,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="inlineStr"/>
@@ -39413,7 +39413,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="inlineStr"/>
@@ -39506,7 +39506,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="inlineStr"/>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="inlineStr"/>
@@ -39692,7 +39692,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="inlineStr"/>
@@ -39785,7 +39785,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="inlineStr"/>
@@ -39878,7 +39878,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="inlineStr"/>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="inlineStr"/>
@@ -40064,7 +40064,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="inlineStr"/>
@@ -40157,7 +40157,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -40250,7 +40250,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="inlineStr"/>
@@ -40343,7 +40343,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="inlineStr"/>
@@ -40436,7 +40436,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="inlineStr"/>
@@ -40529,7 +40529,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -40731,7 +40731,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="inlineStr"/>
@@ -40824,7 +40824,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -40917,7 +40917,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="inlineStr"/>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="inlineStr"/>
@@ -41103,7 +41103,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="inlineStr"/>
@@ -41196,7 +41196,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="inlineStr"/>
@@ -41289,7 +41289,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="inlineStr"/>
@@ -41382,7 +41382,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="inlineStr"/>
@@ -41475,7 +41475,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="inlineStr"/>
@@ -41568,7 +41568,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="inlineStr"/>
@@ -41661,7 +41661,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="inlineStr"/>
@@ -41754,7 +41754,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="inlineStr"/>
@@ -41847,7 +41847,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="inlineStr"/>
@@ -41940,7 +41940,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="inlineStr"/>
@@ -42033,7 +42033,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -42126,7 +42126,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -42219,7 +42219,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -42312,7 +42312,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -42405,7 +42405,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -42498,7 +42498,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42591,7 +42591,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="inlineStr"/>
@@ -42684,7 +42684,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="inlineStr"/>
@@ -42777,7 +42777,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="inlineStr"/>
@@ -42870,7 +42870,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="inlineStr"/>
@@ -42963,7 +42963,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="inlineStr"/>
@@ -43056,7 +43056,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -43149,7 +43149,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="inlineStr"/>
@@ -43242,7 +43242,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -43341,7 +43341,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="inlineStr"/>
@@ -43434,7 +43434,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="inlineStr"/>
@@ -43527,7 +43527,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="inlineStr"/>
@@ -43620,7 +43620,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="inlineStr"/>
@@ -43713,7 +43713,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="inlineStr"/>
@@ -43806,7 +43806,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="inlineStr"/>
@@ -43899,7 +43899,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="inlineStr"/>
@@ -44192,7 +44192,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="inlineStr"/>
@@ -44285,7 +44285,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="inlineStr"/>
@@ -44378,7 +44378,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="inlineStr"/>
@@ -44471,7 +44471,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="inlineStr"/>
@@ -44564,7 +44564,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="inlineStr"/>
@@ -44657,7 +44657,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="inlineStr"/>
@@ -44754,7 +44754,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="inlineStr"/>
@@ -44851,7 +44851,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="inlineStr"/>
@@ -44948,7 +44948,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="inlineStr"/>
@@ -45045,7 +45045,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="inlineStr"/>
@@ -45142,7 +45142,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="inlineStr"/>
@@ -45239,7 +45239,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="inlineStr"/>
@@ -45336,7 +45336,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="inlineStr"/>
@@ -45433,7 +45433,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="inlineStr"/>
@@ -45530,7 +45530,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="inlineStr"/>
@@ -45627,7 +45627,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="inlineStr"/>
@@ -45724,7 +45724,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -45821,7 +45821,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="n">
@@ -45922,7 +45922,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="inlineStr"/>
@@ -46116,7 +46116,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="inlineStr"/>
@@ -46213,7 +46213,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="inlineStr"/>
@@ -46310,7 +46310,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="inlineStr"/>
@@ -46407,7 +46407,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="inlineStr"/>
@@ -46504,7 +46504,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="inlineStr"/>
@@ -46601,7 +46601,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="inlineStr"/>
@@ -46698,7 +46698,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="inlineStr"/>
@@ -46795,7 +46795,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="inlineStr"/>
@@ -46892,7 +46892,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -46989,7 +46989,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="n">
@@ -47185,7 +47185,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="n">
@@ -47284,7 +47284,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="inlineStr"/>
@@ -47381,7 +47381,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="inlineStr"/>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="inlineStr"/>
@@ -47575,7 +47575,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="inlineStr"/>
@@ -47672,7 +47672,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="inlineStr"/>
@@ -47769,7 +47769,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="inlineStr"/>
@@ -47866,7 +47866,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="inlineStr"/>
@@ -47963,7 +47963,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="inlineStr"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="inlineStr"/>
@@ -48157,7 +48157,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="inlineStr"/>
@@ -48254,7 +48254,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="inlineStr"/>
@@ -48351,7 +48351,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="inlineStr"/>
@@ -48448,7 +48448,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="inlineStr"/>
@@ -48545,7 +48545,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="inlineStr"/>
@@ -48642,7 +48642,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="inlineStr"/>
@@ -48739,7 +48739,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="inlineStr"/>
@@ -48836,7 +48836,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="inlineStr"/>
@@ -48933,7 +48933,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="inlineStr"/>
@@ -49030,7 +49030,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="inlineStr"/>
@@ -49127,7 +49127,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="inlineStr"/>
@@ -49224,7 +49224,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="inlineStr"/>
@@ -49321,7 +49321,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="inlineStr"/>
@@ -49418,7 +49418,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="inlineStr"/>
@@ -49515,7 +49515,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="inlineStr"/>
@@ -49612,7 +49612,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="inlineStr"/>
@@ -49709,7 +49709,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="inlineStr"/>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="inlineStr"/>
@@ -49903,7 +49903,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="inlineStr"/>
@@ -50000,7 +50000,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="inlineStr"/>
@@ -50097,7 +50097,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="inlineStr"/>
@@ -50194,7 +50194,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="inlineStr"/>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="inlineStr"/>
@@ -50388,7 +50388,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="inlineStr"/>
@@ -50485,7 +50485,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="inlineStr"/>
@@ -50582,7 +50582,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="inlineStr"/>
@@ -50679,7 +50679,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="inlineStr"/>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="inlineStr"/>
@@ -50873,7 +50873,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="inlineStr"/>
@@ -50970,7 +50970,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="inlineStr"/>
@@ -51067,7 +51067,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="inlineStr"/>
@@ -51164,7 +51164,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="inlineStr"/>
@@ -51261,7 +51261,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="inlineStr"/>
@@ -51358,7 +51358,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="inlineStr"/>
@@ -51455,7 +51455,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="inlineStr"/>
@@ -51552,7 +51552,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="inlineStr"/>
@@ -51649,7 +51649,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="inlineStr"/>
@@ -51746,7 +51746,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="inlineStr"/>
@@ -51843,7 +51843,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="inlineStr"/>
@@ -51940,7 +51940,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="inlineStr"/>
@@ -52037,7 +52037,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="inlineStr"/>
@@ -52134,7 +52134,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="inlineStr"/>
@@ -52231,7 +52231,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="inlineStr"/>
@@ -52328,7 +52328,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="inlineStr"/>
@@ -52425,7 +52425,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="inlineStr"/>
@@ -52522,7 +52522,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="inlineStr"/>
@@ -52619,7 +52619,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T547" t="inlineStr"/>
@@ -52716,7 +52716,7 @@
       </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T548" t="inlineStr"/>
@@ -52813,7 +52813,7 @@
       </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T549" t="inlineStr"/>
@@ -52910,7 +52910,7 @@
       </c>
       <c r="S550" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T550" t="inlineStr"/>
@@ -53007,7 +53007,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T551" t="inlineStr"/>
@@ -53104,7 +53104,7 @@
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T552" t="inlineStr"/>
@@ -53201,7 +53201,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T553" t="inlineStr"/>
@@ -53298,7 +53298,7 @@
       </c>
       <c r="S554" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T554" t="inlineStr"/>
@@ -53395,7 +53395,7 @@
       </c>
       <c r="S555" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T555" t="inlineStr"/>
@@ -53492,7 +53492,7 @@
       </c>
       <c r="S556" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T556" t="inlineStr"/>
@@ -53589,7 +53589,7 @@
       </c>
       <c r="S557" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T557" t="inlineStr"/>
@@ -53686,7 +53686,7 @@
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T558" t="inlineStr"/>
@@ -53783,7 +53783,7 @@
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T559" t="inlineStr"/>
@@ -53880,7 +53880,7 @@
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T560" t="inlineStr"/>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T561" t="inlineStr"/>
@@ -54074,7 +54074,7 @@
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T562" t="inlineStr"/>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T563" t="inlineStr"/>
@@ -54268,7 +54268,7 @@
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T564" t="inlineStr"/>
@@ -54365,7 +54365,7 @@
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T565" t="inlineStr"/>
@@ -54462,7 +54462,7 @@
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T566" t="inlineStr"/>
@@ -54559,7 +54559,7 @@
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T567" t="inlineStr"/>
@@ -54656,7 +54656,7 @@
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T568" t="inlineStr"/>
@@ -54753,7 +54753,7 @@
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T569" t="inlineStr"/>
@@ -54850,7 +54850,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T570" t="inlineStr"/>
@@ -54947,7 +54947,7 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T571" t="inlineStr"/>
@@ -55044,7 +55044,7 @@
       </c>
       <c r="S572" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T572" t="inlineStr"/>
@@ -55141,7 +55141,7 @@
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T573" t="inlineStr"/>
@@ -55238,7 +55238,7 @@
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T574" t="inlineStr"/>
@@ -55335,7 +55335,7 @@
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T575" t="inlineStr"/>
@@ -55432,7 +55432,7 @@
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T576" t="inlineStr"/>
@@ -55529,7 +55529,7 @@
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T577" t="inlineStr"/>
@@ -55626,7 +55626,7 @@
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T578" t="inlineStr"/>
@@ -55723,7 +55723,7 @@
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T579" t="inlineStr"/>
@@ -55820,7 +55820,7 @@
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T580" t="inlineStr"/>
@@ -55917,7 +55917,7 @@
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T581" t="inlineStr"/>
@@ -56014,7 +56014,7 @@
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T582" t="inlineStr"/>
@@ -56111,7 +56111,7 @@
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T583" t="inlineStr"/>
@@ -56208,7 +56208,7 @@
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T584" t="inlineStr"/>
@@ -56305,7 +56305,7 @@
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T585" t="inlineStr"/>
@@ -56402,7 +56402,7 @@
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T586" t="inlineStr"/>
@@ -56499,7 +56499,7 @@
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T587" t="inlineStr"/>
@@ -56596,7 +56596,7 @@
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T588" t="inlineStr"/>
@@ -56693,7 +56693,7 @@
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T589" t="inlineStr"/>
@@ -56790,7 +56790,7 @@
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T590" t="inlineStr"/>
@@ -56887,7 +56887,7 @@
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T591" t="inlineStr"/>
@@ -56984,7 +56984,7 @@
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T592" t="inlineStr"/>
@@ -57081,7 +57081,7 @@
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T593" t="inlineStr"/>
@@ -57178,7 +57178,7 @@
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T594" t="inlineStr"/>
@@ -57275,7 +57275,7 @@
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T595" t="inlineStr"/>
@@ -57372,7 +57372,7 @@
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T596" t="inlineStr"/>
@@ -57469,7 +57469,7 @@
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T597" t="inlineStr"/>
@@ -57566,7 +57566,7 @@
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T598" t="inlineStr"/>
@@ -57663,7 +57663,7 @@
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T599" t="inlineStr"/>
@@ -57760,7 +57760,7 @@
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T600" t="inlineStr"/>
@@ -57857,7 +57857,7 @@
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T601" t="inlineStr"/>
@@ -57954,7 +57954,7 @@
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T602" t="inlineStr"/>
@@ -58051,7 +58051,7 @@
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T603" t="inlineStr"/>
@@ -58148,7 +58148,7 @@
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T604" t="inlineStr"/>
@@ -58245,7 +58245,7 @@
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T605" t="inlineStr"/>
@@ -58342,7 +58342,7 @@
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T606" t="inlineStr"/>
@@ -58439,7 +58439,7 @@
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T607" t="inlineStr"/>
@@ -58536,7 +58536,7 @@
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T608" t="inlineStr"/>
@@ -58633,7 +58633,7 @@
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T609" t="inlineStr"/>
@@ -58730,7 +58730,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T610" t="inlineStr"/>
@@ -58827,7 +58827,7 @@
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T611" t="inlineStr"/>
@@ -58924,7 +58924,7 @@
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T612" t="inlineStr"/>
@@ -59021,7 +59021,7 @@
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T613" t="inlineStr"/>
@@ -59118,7 +59118,7 @@
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T614" t="inlineStr"/>
@@ -59215,7 +59215,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T615" t="inlineStr"/>
@@ -59312,7 +59312,7 @@
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T616" t="inlineStr"/>
@@ -59409,7 +59409,7 @@
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T617" t="inlineStr"/>
@@ -59506,7 +59506,7 @@
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T618" t="inlineStr"/>
@@ -59603,7 +59603,7 @@
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T619" t="inlineStr"/>
@@ -59700,7 +59700,7 @@
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T620" t="inlineStr"/>
@@ -59797,7 +59797,7 @@
       </c>
       <c r="S621" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T621" t="inlineStr"/>
@@ -59894,7 +59894,7 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T622" t="inlineStr"/>
@@ -59991,7 +59991,7 @@
       </c>
       <c r="S623" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T623" t="inlineStr"/>
@@ -60084,7 +60084,7 @@
       </c>
       <c r="S624" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T624" t="inlineStr"/>
@@ -60177,7 +60177,7 @@
       </c>
       <c r="S625" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T625" t="inlineStr"/>
@@ -60270,7 +60270,7 @@
       </c>
       <c r="S626" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T626" t="inlineStr"/>
@@ -60363,7 +60363,7 @@
       </c>
       <c r="S627" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T627" t="inlineStr"/>
@@ -60456,7 +60456,7 @@
       </c>
       <c r="S628" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T628" t="inlineStr"/>
@@ -60549,7 +60549,7 @@
       </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T629" t="inlineStr"/>
@@ -60642,7 +60642,7 @@
       </c>
       <c r="S630" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T630" t="inlineStr"/>
@@ -60735,7 +60735,7 @@
       </c>
       <c r="S631" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T631" t="inlineStr"/>
@@ -60828,7 +60828,7 @@
       </c>
       <c r="S632" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T632" t="inlineStr"/>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S633" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T633" t="inlineStr"/>
@@ -61014,7 +61014,7 @@
       </c>
       <c r="S634" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T634" t="inlineStr"/>
@@ -61107,7 +61107,7 @@
       </c>
       <c r="S635" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T635" t="inlineStr"/>
@@ -61200,7 +61200,7 @@
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T636" t="inlineStr"/>
@@ -61293,7 +61293,7 @@
       </c>
       <c r="S637" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T637" t="inlineStr"/>
@@ -61386,7 +61386,7 @@
       </c>
       <c r="S638" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T638" t="inlineStr"/>
@@ -61479,7 +61479,7 @@
       </c>
       <c r="S639" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T639" t="inlineStr"/>
@@ -61572,7 +61572,7 @@
       </c>
       <c r="S640" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T640" t="inlineStr"/>
@@ -61665,7 +61665,7 @@
       </c>
       <c r="S641" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T641" t="inlineStr"/>
@@ -61758,7 +61758,7 @@
       </c>
       <c r="S642" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T642" t="inlineStr"/>
@@ -61851,7 +61851,7 @@
       </c>
       <c r="S643" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T643" t="inlineStr"/>
@@ -61944,7 +61944,7 @@
       </c>
       <c r="S644" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T644" t="inlineStr"/>
@@ -62041,7 +62041,7 @@
       </c>
       <c r="S645" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T645" t="inlineStr"/>
@@ -62138,7 +62138,7 @@
       </c>
       <c r="S646" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T646" t="inlineStr"/>
@@ -62235,7 +62235,7 @@
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T647" t="inlineStr"/>
@@ -62332,7 +62332,7 @@
       </c>
       <c r="S648" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T648" t="inlineStr"/>
@@ -62429,7 +62429,7 @@
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T649" t="inlineStr"/>
@@ -62526,7 +62526,7 @@
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T650" t="inlineStr"/>
@@ -62623,7 +62623,7 @@
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T651" t="inlineStr"/>
@@ -62720,7 +62720,7 @@
       </c>
       <c r="S652" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T652" t="inlineStr"/>
@@ -62817,7 +62817,7 @@
       </c>
       <c r="S653" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T653" t="inlineStr"/>
@@ -62914,7 +62914,7 @@
       </c>
       <c r="S654" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T654" t="inlineStr"/>
@@ -63011,7 +63011,7 @@
       </c>
       <c r="S655" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T655" t="inlineStr"/>
@@ -63108,7 +63108,7 @@
       </c>
       <c r="S656" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T656" t="n">
@@ -63207,7 +63207,7 @@
       </c>
       <c r="S657" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T657" t="n">
@@ -63306,7 +63306,7 @@
       </c>
       <c r="S658" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T658" t="inlineStr"/>
@@ -63399,7 +63399,7 @@
       </c>
       <c r="S659" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T659" t="inlineStr"/>
@@ -63492,7 +63492,7 @@
       </c>
       <c r="S660" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T660" t="inlineStr"/>
@@ -63585,7 +63585,7 @@
       </c>
       <c r="S661" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T661" t="inlineStr"/>
@@ -63678,7 +63678,7 @@
       </c>
       <c r="S662" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T662" t="inlineStr"/>
@@ -63771,7 +63771,7 @@
       </c>
       <c r="S663" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T663" t="inlineStr"/>
@@ -63864,7 +63864,7 @@
       </c>
       <c r="S664" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T664" t="inlineStr"/>
@@ -63961,7 +63961,7 @@
       </c>
       <c r="S665" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T665" t="inlineStr"/>
@@ -64058,7 +64058,7 @@
       </c>
       <c r="S666" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T666" t="inlineStr"/>
@@ -64155,7 +64155,7 @@
       </c>
       <c r="S667" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T667" t="inlineStr"/>
@@ -64252,7 +64252,7 @@
       </c>
       <c r="S668" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T668" t="inlineStr"/>
@@ -64349,7 +64349,7 @@
       </c>
       <c r="S669" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T669" t="inlineStr"/>
@@ -64446,7 +64446,7 @@
       </c>
       <c r="S670" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T670" t="inlineStr"/>
@@ -64543,7 +64543,7 @@
       </c>
       <c r="S671" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T671" t="inlineStr"/>
@@ -64640,7 +64640,7 @@
       </c>
       <c r="S672" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T672" t="inlineStr"/>
@@ -64737,7 +64737,7 @@
       </c>
       <c r="S673" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T673" t="inlineStr"/>
@@ -64834,7 +64834,7 @@
       </c>
       <c r="S674" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T674" t="inlineStr"/>
@@ -64931,7 +64931,7 @@
       </c>
       <c r="S675" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T675" t="inlineStr"/>
@@ -65028,7 +65028,7 @@
       </c>
       <c r="S676" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T676" t="inlineStr"/>
@@ -65125,7 +65125,7 @@
       </c>
       <c r="S677" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T677" t="inlineStr"/>
@@ -65222,7 +65222,7 @@
       </c>
       <c r="S678" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T678" t="inlineStr"/>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="S679" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T679" t="inlineStr"/>
@@ -65416,7 +65416,7 @@
       </c>
       <c r="S680" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T680" t="inlineStr"/>
@@ -65513,7 +65513,7 @@
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T681" t="inlineStr"/>
@@ -65610,7 +65610,7 @@
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T682" t="inlineStr"/>
@@ -65707,7 +65707,7 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T683" t="inlineStr"/>
@@ -65804,7 +65804,7 @@
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T684" t="inlineStr"/>
@@ -65901,7 +65901,7 @@
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T685" t="inlineStr"/>
@@ -65998,7 +65998,7 @@
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T686" t="inlineStr"/>
@@ -66095,7 +66095,7 @@
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T687" t="inlineStr"/>
@@ -66192,7 +66192,7 @@
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T688" t="inlineStr"/>
@@ -66289,7 +66289,7 @@
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T689" t="inlineStr"/>
@@ -66386,7 +66386,7 @@
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T690" t="inlineStr"/>
@@ -66483,7 +66483,7 @@
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T691" t="inlineStr"/>
@@ -66580,7 +66580,7 @@
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T692" t="inlineStr"/>
@@ -66677,7 +66677,7 @@
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T693" t="inlineStr"/>
@@ -66774,7 +66774,7 @@
       </c>
       <c r="S694" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T694" t="inlineStr"/>
@@ -66871,7 +66871,7 @@
       </c>
       <c r="S695" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T695" t="inlineStr"/>
@@ -66968,7 +66968,7 @@
       </c>
       <c r="S696" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T696" t="inlineStr"/>
@@ -67065,7 +67065,7 @@
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T697" t="inlineStr"/>
@@ -67162,7 +67162,7 @@
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T698" t="inlineStr"/>
@@ -67259,7 +67259,7 @@
       </c>
       <c r="S699" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T699" t="inlineStr"/>
@@ -67356,7 +67356,7 @@
       </c>
       <c r="S700" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T700" t="inlineStr"/>
@@ -67453,7 +67453,7 @@
       </c>
       <c r="S701" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T701" t="inlineStr"/>
@@ -67550,7 +67550,7 @@
       </c>
       <c r="S702" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T702" t="inlineStr"/>
@@ -67647,7 +67647,7 @@
       </c>
       <c r="S703" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T703" t="inlineStr"/>
@@ -67748,7 +67748,7 @@
       </c>
       <c r="S704" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T704" t="inlineStr"/>
@@ -67845,7 +67845,7 @@
       </c>
       <c r="S705" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T705" t="inlineStr"/>
@@ -67942,7 +67942,7 @@
       </c>
       <c r="S706" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T706" t="inlineStr"/>
@@ -68039,7 +68039,7 @@
       </c>
       <c r="S707" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T707" t="inlineStr"/>
@@ -68136,7 +68136,7 @@
       </c>
       <c r="S708" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T708" t="inlineStr"/>
@@ -68233,7 +68233,7 @@
       </c>
       <c r="S709" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T709" t="inlineStr"/>
@@ -68330,7 +68330,7 @@
       </c>
       <c r="S710" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T710" t="inlineStr"/>
@@ -68427,7 +68427,7 @@
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T711" t="inlineStr"/>
@@ -68524,7 +68524,7 @@
       </c>
       <c r="S712" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T712" t="inlineStr"/>
@@ -68625,7 +68625,7 @@
       </c>
       <c r="S713" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T713" t="inlineStr"/>
@@ -68722,7 +68722,7 @@
       </c>
       <c r="S714" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T714" t="inlineStr"/>
@@ -68823,7 +68823,7 @@
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T715" t="inlineStr"/>
@@ -68924,7 +68924,7 @@
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T716" t="inlineStr"/>
@@ -69025,7 +69025,7 @@
       </c>
       <c r="S717" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T717" t="inlineStr"/>
@@ -69126,7 +69126,7 @@
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T718" t="inlineStr"/>
@@ -69227,7 +69227,7 @@
       </c>
       <c r="S719" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T719" t="inlineStr"/>
@@ -69324,7 +69324,7 @@
       </c>
       <c r="S720" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T720" t="inlineStr"/>
@@ -69421,7 +69421,7 @@
       </c>
       <c r="S721" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T721" t="inlineStr"/>
@@ -69518,7 +69518,7 @@
       </c>
       <c r="S722" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T722" t="inlineStr"/>
@@ -69615,7 +69615,7 @@
       </c>
       <c r="S723" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T723" t="inlineStr"/>
@@ -69712,7 +69712,7 @@
       </c>
       <c r="S724" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T724" t="inlineStr"/>
@@ -69805,7 +69805,7 @@
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T725" t="inlineStr"/>
@@ -69898,7 +69898,7 @@
       </c>
       <c r="S726" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T726" t="inlineStr"/>
@@ -69991,7 +69991,7 @@
       </c>
       <c r="S727" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T727" t="inlineStr"/>
@@ -70084,7 +70084,7 @@
       </c>
       <c r="S728" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T728" t="inlineStr"/>
@@ -70177,7 +70177,7 @@
       </c>
       <c r="S729" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T729" t="inlineStr"/>
@@ -70270,7 +70270,7 @@
       </c>
       <c r="S730" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T730" t="inlineStr"/>
@@ -70371,7 +70371,7 @@
       </c>
       <c r="S731" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T731" t="inlineStr"/>
@@ -70468,7 +70468,7 @@
       </c>
       <c r="S732" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T732" t="inlineStr"/>
@@ -70569,7 +70569,7 @@
       </c>
       <c r="S733" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T733" t="inlineStr"/>
@@ -70670,7 +70670,7 @@
       </c>
       <c r="S734" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T734" t="inlineStr"/>
@@ -70771,7 +70771,7 @@
       </c>
       <c r="S735" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T735" t="inlineStr"/>
@@ -70872,7 +70872,7 @@
       </c>
       <c r="S736" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T736" t="inlineStr"/>
@@ -70973,7 +70973,7 @@
       </c>
       <c r="S737" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T737" t="inlineStr"/>
@@ -71070,7 +71070,7 @@
       </c>
       <c r="S738" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T738" t="inlineStr"/>
@@ -71167,7 +71167,7 @@
       </c>
       <c r="S739" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T739" t="inlineStr"/>
@@ -71264,7 +71264,7 @@
       </c>
       <c r="S740" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T740" t="inlineStr"/>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S741" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T741" t="inlineStr"/>
@@ -71458,7 +71458,7 @@
       </c>
       <c r="S742" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T742" t="inlineStr"/>
@@ -71555,7 +71555,7 @@
       </c>
       <c r="S743" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T743" t="inlineStr"/>
@@ -71652,7 +71652,7 @@
       </c>
       <c r="S744" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T744" t="inlineStr"/>
@@ -71749,7 +71749,7 @@
       </c>
       <c r="S745" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T745" t="inlineStr"/>
@@ -71846,7 +71846,7 @@
       </c>
       <c r="S746" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T746" t="inlineStr"/>
@@ -71943,7 +71943,7 @@
       </c>
       <c r="S747" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T747" t="inlineStr"/>
@@ -72040,7 +72040,7 @@
       </c>
       <c r="S748" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T748" t="inlineStr"/>
@@ -72137,7 +72137,7 @@
       </c>
       <c r="S749" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T749" t="inlineStr"/>
@@ -72234,7 +72234,7 @@
       </c>
       <c r="S750" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T750" t="inlineStr"/>
@@ -72331,7 +72331,7 @@
       </c>
       <c r="S751" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T751" t="inlineStr"/>
@@ -72428,7 +72428,7 @@
       </c>
       <c r="S752" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T752" t="inlineStr"/>
@@ -72525,7 +72525,7 @@
       </c>
       <c r="S753" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T753" t="inlineStr"/>
@@ -72622,7 +72622,7 @@
       </c>
       <c r="S754" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T754" t="inlineStr"/>
@@ -72719,7 +72719,7 @@
       </c>
       <c r="S755" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T755" t="inlineStr"/>
@@ -72816,7 +72816,7 @@
       </c>
       <c r="S756" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T756" t="inlineStr"/>
@@ -72913,7 +72913,7 @@
       </c>
       <c r="S757" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T757" t="inlineStr"/>
@@ -73010,7 +73010,7 @@
       </c>
       <c r="S758" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T758" t="inlineStr"/>
@@ -73107,7 +73107,7 @@
       </c>
       <c r="S759" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T759" t="inlineStr"/>
@@ -73204,7 +73204,7 @@
       </c>
       <c r="S760" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T760" t="inlineStr"/>
@@ -73301,7 +73301,7 @@
       </c>
       <c r="S761" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T761" t="inlineStr"/>
@@ -73398,7 +73398,7 @@
       </c>
       <c r="S762" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T762" t="inlineStr"/>
@@ -73495,7 +73495,7 @@
       </c>
       <c r="S763" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T763" t="inlineStr"/>
@@ -73592,7 +73592,7 @@
       </c>
       <c r="S764" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T764" t="inlineStr"/>
@@ -73689,7 +73689,7 @@
       </c>
       <c r="S765" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T765" t="inlineStr"/>
@@ -73786,7 +73786,7 @@
       </c>
       <c r="S766" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T766" t="inlineStr"/>
@@ -73879,7 +73879,7 @@
       </c>
       <c r="S767" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T767" t="inlineStr"/>
@@ -73972,7 +73972,7 @@
       </c>
       <c r="S768" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T768" t="inlineStr"/>
@@ -74065,7 +74065,7 @@
       </c>
       <c r="S769" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T769" t="inlineStr"/>
@@ -74158,7 +74158,7 @@
       </c>
       <c r="S770" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T770" t="inlineStr"/>
@@ -74251,7 +74251,7 @@
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T771" t="inlineStr"/>
@@ -74344,7 +74344,7 @@
       </c>
       <c r="S772" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T772" t="inlineStr"/>
@@ -74437,7 +74437,7 @@
       </c>
       <c r="S773" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T773" t="inlineStr"/>
@@ -74530,7 +74530,7 @@
       </c>
       <c r="S774" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T774" t="inlineStr"/>
@@ -74623,7 +74623,7 @@
       </c>
       <c r="S775" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T775" t="inlineStr"/>
@@ -74716,7 +74716,7 @@
       </c>
       <c r="S776" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T776" t="inlineStr"/>
@@ -74809,7 +74809,7 @@
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T777" t="inlineStr"/>
@@ -74902,7 +74902,7 @@
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T778" t="inlineStr"/>
@@ -74995,7 +74995,7 @@
       </c>
       <c r="S779" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T779" t="inlineStr"/>
@@ -75088,7 +75088,7 @@
       </c>
       <c r="S780" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T780" t="inlineStr"/>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S781" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T781" t="inlineStr"/>
@@ -75274,7 +75274,7 @@
       </c>
       <c r="S782" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T782" t="inlineStr"/>
@@ -75367,7 +75367,7 @@
       </c>
       <c r="S783" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T783" t="inlineStr"/>
@@ -75460,7 +75460,7 @@
       </c>
       <c r="S784" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T784" t="inlineStr"/>
@@ -75553,7 +75553,7 @@
       </c>
       <c r="S785" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T785" t="inlineStr"/>
@@ -75646,7 +75646,7 @@
       </c>
       <c r="S786" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T786" t="inlineStr"/>
@@ -75739,7 +75739,7 @@
       </c>
       <c r="S787" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T787" t="inlineStr"/>
@@ -75832,7 +75832,7 @@
       </c>
       <c r="S788" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T788" t="inlineStr"/>
@@ -75925,7 +75925,7 @@
       </c>
       <c r="S789" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T789" t="inlineStr"/>
@@ -76018,7 +76018,7 @@
       </c>
       <c r="S790" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T790" t="inlineStr"/>
@@ -76111,7 +76111,7 @@
       </c>
       <c r="S791" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T791" t="inlineStr"/>
@@ -76204,7 +76204,7 @@
       </c>
       <c r="S792" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T792" t="inlineStr"/>
@@ -76297,7 +76297,7 @@
       </c>
       <c r="S793" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T793" t="inlineStr"/>
@@ -76390,7 +76390,7 @@
       </c>
       <c r="S794" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T794" t="inlineStr"/>
@@ -76483,7 +76483,7 @@
       </c>
       <c r="S795" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T795" t="inlineStr"/>
@@ -76576,7 +76576,7 @@
       </c>
       <c r="S796" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T796" t="inlineStr"/>
@@ -76669,7 +76669,7 @@
       </c>
       <c r="S797" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T797" t="inlineStr"/>
@@ -76762,7 +76762,7 @@
       </c>
       <c r="S798" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T798" t="inlineStr"/>
@@ -76855,7 +76855,7 @@
       </c>
       <c r="S799" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T799" t="inlineStr"/>
@@ -76948,7 +76948,7 @@
       </c>
       <c r="S800" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T800" t="inlineStr"/>
@@ -77041,7 +77041,7 @@
       </c>
       <c r="S801" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T801" t="inlineStr"/>
@@ -77134,7 +77134,7 @@
       </c>
       <c r="S802" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T802" t="inlineStr"/>
@@ -77227,7 +77227,7 @@
       </c>
       <c r="S803" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T803" t="inlineStr"/>
@@ -77320,7 +77320,7 @@
       </c>
       <c r="S804" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T804" t="inlineStr"/>
@@ -77413,7 +77413,7 @@
       </c>
       <c r="S805" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T805" t="inlineStr"/>
@@ -77506,7 +77506,7 @@
       </c>
       <c r="S806" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T806" t="inlineStr"/>
@@ -77599,7 +77599,7 @@
       </c>
       <c r="S807" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T807" t="inlineStr"/>
@@ -77692,7 +77692,7 @@
       </c>
       <c r="S808" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T808" t="inlineStr"/>
@@ -77785,7 +77785,7 @@
       </c>
       <c r="S809" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T809" t="inlineStr"/>
@@ -77878,7 +77878,7 @@
       </c>
       <c r="S810" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T810" t="inlineStr"/>
@@ -77971,7 +77971,7 @@
       </c>
       <c r="S811" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T811" t="inlineStr"/>
@@ -78064,7 +78064,7 @@
       </c>
       <c r="S812" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T812" t="inlineStr"/>
@@ -78157,7 +78157,7 @@
       </c>
       <c r="S813" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T813" t="inlineStr"/>
@@ -78250,7 +78250,7 @@
       </c>
       <c r="S814" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T814" t="inlineStr"/>
@@ -78343,7 +78343,7 @@
       </c>
       <c r="S815" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T815" t="inlineStr"/>
@@ -78436,7 +78436,7 @@
       </c>
       <c r="S816" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T816" t="inlineStr"/>
@@ -78529,7 +78529,7 @@
       </c>
       <c r="S817" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T817" t="inlineStr"/>
@@ -78622,7 +78622,7 @@
       </c>
       <c r="S818" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T818" t="inlineStr"/>
@@ -78715,7 +78715,7 @@
       </c>
       <c r="S819" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T819" t="inlineStr"/>
@@ -78808,7 +78808,7 @@
       </c>
       <c r="S820" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T820" t="inlineStr"/>
@@ -78901,7 +78901,7 @@
       </c>
       <c r="S821" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T821" t="inlineStr"/>
@@ -78994,7 +78994,7 @@
       </c>
       <c r="S822" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T822" t="inlineStr"/>
@@ -79087,7 +79087,7 @@
       </c>
       <c r="S823" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T823" t="inlineStr"/>
@@ -79180,7 +79180,7 @@
       </c>
       <c r="S824" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T824" t="inlineStr"/>
@@ -79273,7 +79273,7 @@
       </c>
       <c r="S825" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T825" t="inlineStr"/>
@@ -79366,7 +79366,7 @@
       </c>
       <c r="S826" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T826" t="inlineStr"/>
@@ -79459,7 +79459,7 @@
       </c>
       <c r="S827" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T827" t="inlineStr"/>
@@ -79552,7 +79552,7 @@
       </c>
       <c r="S828" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T828" t="inlineStr"/>
@@ -79645,7 +79645,7 @@
       </c>
       <c r="S829" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T829" t="inlineStr"/>
